--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -662,10 +662,10 @@
         <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="N2" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="M6" t="n">
         <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI14"/>
+  <dimension ref="A1:AI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,80 +1369,80 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.3</v>
+        <v>1.96</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>2.93</v>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>45995.54166666666</v>
+        <v>45995.5</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>45995.58333333334</v>
+        <v>45995.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45995.625</v>
+        <v>45995.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>45995.64583333334</v>
+        <v>45995.625</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>45995.66666666666</v>
+        <v>45995.64583333334</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>45995.70833333334</v>
+        <v>45995.66666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,116 +2046,235 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="n">
+        <v>45995.70833333334</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Cruzeiro</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Botafogo</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="n">
         <v>45995.8125</v>
       </c>
     </row>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4.15</v>
+        <v>3.89</v>
       </c>
       <c r="N2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>3.16</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,10 +1531,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA9" t="n">
         <v>2</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,80 +1488,80 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.5</v>
+        <v>1.96</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>2.93</v>
       </c>
       <c r="N9" t="n">
-        <v>1.53</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>45995.54166666666</v>
+        <v>45995.5</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45995.58333333334</v>
+        <v>45995.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>45995.625</v>
+        <v>45995.58333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>45995.64583333334</v>
+        <v>45995.625</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>45995.66666666666</v>
+        <v>45995.64583333334</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>45995.70833333334</v>
+        <v>45995.66666666666</v>
       </c>
     </row>
     <row r="15">
@@ -2165,116 +2165,235 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="n">
+        <v>45995.70833333334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Cruzeiro</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Botafogo</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="3" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3" t="n">
         <v>45995.8125</v>
       </c>
     </row>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>3.89</v>
+        <v>4.25</v>
       </c>
       <c r="N2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.41</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45995.33333333334</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="M6" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45995.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1620,34 +1620,34 @@
         <v>1.53</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
         <v>1.3</v>
@@ -1662,22 +1662,22 @@
         <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1739,40 +1739,40 @@
         <v>1.69</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="AA11" t="n">
         <v>1.85</v>
@@ -1781,22 +1781,22 @@
         <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.58333333334</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45995.66666666666</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45995.70833333334</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1745,7 +1745,7 @@
         <v>2.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="R11" t="n">
         <v>1.3</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -659,67 +659,67 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4.25</v>
+        <v>3.89</v>
       </c>
       <c r="N2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O2" t="n">
-        <v>7.12</v>
+        <v>7.7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
         <v>6.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.98</v>
+        <v>3.06</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AG2" t="n">
         <v>1.22</v>
@@ -1135,37 +1135,37 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="N6" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="U6" t="n">
         <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
@@ -1180,28 +1180,28 @@
         <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.98</v>
+        <v>3.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
         <v>1.27</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45995.4375</v>
@@ -1623,10 +1623,10 @@
         <v>6.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="R10" t="n">
         <v>1.41</v>
@@ -1635,13 +1635,13 @@
         <v>2.66</v>
       </c>
       <c r="T10" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
         <v>1.05</v>
@@ -1665,19 +1665,19 @@
         <v>3.52</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
         <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1739,40 +1739,40 @@
         <v>1.69</v>
       </c>
       <c r="O11" t="n">
-        <v>5.15</v>
+        <v>4.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
         <v>2.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.23</v>
+        <v>2.91</v>
       </c>
       <c r="T11" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
         <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
         <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
         <v>1.85</v>
@@ -1781,22 +1781,22 @@
         <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.07</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.58333333334</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
         <v>1.44</v>
@@ -1992,19 +1992,19 @@
         <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
         <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
         <v>1.4</v>
@@ -2013,16 +2013,16 @@
         <v>2.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2031,10 +2031,10 @@
         <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45995.64583333334</v>
@@ -2209,67 +2209,67 @@
         <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>6.8</v>
+        <v>6.65</v>
       </c>
       <c r="O15" t="n">
         <v>1.85</v>
       </c>
       <c r="P15" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="T15" t="n">
         <v>2.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V15" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="W15" t="n">
         <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AC15" t="n">
         <v>2.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
         <v>2.63</v>
@@ -2334,40 +2334,40 @@
         <v>3.37</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA16" t="n">
         <v>2.15</v>
@@ -2376,22 +2376,22 @@
         <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45995.8125</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -2087,25 +2087,25 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
         <v>2.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
         <v>3.6</v>
@@ -2117,7 +2117,7 @@
         <v>1.61</v>
       </c>
       <c r="V14" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="W14" t="n">
         <v>1.12</v>
@@ -2126,13 +2126,13 @@
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z14" t="n">
         <v>5.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
         <v>2.42</v>
@@ -2141,7 +2141,7 @@
         <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE14" t="n">
         <v>1.43</v>
@@ -2150,10 +2150,10 @@
         <v>2.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45995.66666666666</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI16"/>
+  <dimension ref="A1:AI17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3.55</v>
       </c>
-      <c r="N10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="O10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V10" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA10" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.52</v>
+        <v>4.37</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="O11" t="n">
-        <v>4.75</v>
+        <v>6.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>45995.58333333334</v>
+        <v>45995.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>45995.625</v>
+        <v>45995.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>45995.64583333334</v>
+        <v>45995.625</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.15</v>
+        <v>1.85</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P14" t="n">
         <v>2</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q14" t="n">
-        <v>2.58</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>2.21</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.15</v>
+        <v>2.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.42</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>4.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.34</v>
+        <v>1.79</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>45995.66666666666</v>
+        <v>45995.64583333334</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>3.15</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
-        <v>6.65</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.85</v>
+        <v>3.45</v>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>2.58</v>
       </c>
       <c r="R15" t="n">
         <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC15" t="n">
         <v>2.25</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.63</v>
+        <v>1.34</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>45995.70833333334</v>
+        <v>45995.66666666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,116 +2284,235 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AI16" s="3" t="n">
+        <v>45995.70833333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Cruzeiro</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Botafogo</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" t="n">
         <v>2.09</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M17" t="n">
         <v>2.9</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N17" t="n">
         <v>3.37</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O17" t="n">
         <v>2.72</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P17" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q17" t="n">
         <v>4.3</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>1.44</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>2.58</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>3.02</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>1.33</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V17" t="n">
         <v>8</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W17" t="n">
         <v>1.02</v>
       </c>
-      <c r="X16" t="n">
+      <c r="X17" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y17" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="Z17" t="n">
         <v>2.99</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA17" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AB17" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AC17" t="n">
         <v>3.54</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AD17" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AE17" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AF17" t="n">
         <v>1.93</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AG17" t="n">
         <v>1.35</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AH17" t="n">
         <v>1.71</v>
       </c>
-      <c r="AI16" s="3" t="n">
+      <c r="AI17" s="3" t="n">
         <v>45995.8125</v>
       </c>
     </row>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="M2" t="n">
-        <v>3.89</v>
+        <v>4.38</v>
       </c>
       <c r="N2" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="O2" t="n">
-        <v>7.7</v>
+        <v>5.8</v>
       </c>
       <c r="P2" t="n">
         <v>2.48</v>
@@ -677,10 +677,10 @@
         <v>1.92</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="T2" t="n">
         <v>2.62</v>
@@ -689,28 +689,28 @@
         <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="AD2" t="n">
         <v>1.32</v>
@@ -719,13 +719,13 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
         <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45995.33333333334</v>
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="M6" t="n">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="P6" t="n">
         <v>1.99</v>
@@ -1156,7 +1156,7 @@
         <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T6" t="n">
         <v>3.27</v>
@@ -1174,22 +1174,22 @@
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
         <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1201,7 +1201,7 @@
         <v>1.27</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45995.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>6.77</v>
       </c>
       <c r="M10" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z10" t="n">
         <v>3</v>
       </c>
-      <c r="N10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V10" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AA10" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC10" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.65</v>
+        <v>1.08</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3.55</v>
       </c>
-      <c r="N11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="O11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.52</v>
+        <v>4.37</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
         <v>1.25</v>
@@ -2239,7 +2239,7 @@
         <v>4.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
@@ -2248,7 +2248,7 @@
         <v>1.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.15</v>
+        <v>5.4</v>
       </c>
       <c r="AA15" t="n">
         <v>1.5</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -662,13 +662,13 @@
         <v>7.1</v>
       </c>
       <c r="M2" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="O2" t="n">
-        <v>5.8</v>
+        <v>5.22</v>
       </c>
       <c r="P2" t="n">
         <v>2.48</v>
@@ -680,10 +680,10 @@
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="T2" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
         <v>1.42</v>
@@ -707,7 +707,7 @@
         <v>1.84</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AC2" t="n">
         <v>3.04</v>
@@ -719,13 +719,13 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG2" t="n">
         <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45995.33333333334</v>
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="P6" t="n">
         <v>1.99</v>
@@ -1156,10 +1156,10 @@
         <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
         <v>1.3</v>
@@ -1168,7 +1168,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
@@ -1180,28 +1180,28 @@
         <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
         <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG6" t="n">
         <v>1.27</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45995.4375</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.77</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.79</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.48</v>
+        <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.07</v>
+        <v>3.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>9.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.56</v>
+        <v>4.37</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="M11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3</v>
       </c>
-      <c r="N11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC11" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.65</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1870,13 +1870,13 @@
         <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="T12" t="n">
         <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V12" t="n">
         <v>6</v>
@@ -1885,13 +1885,13 @@
         <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA12" t="n">
         <v>1.85</v>
@@ -1900,22 +1900,22 @@
         <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE12" t="n">
         <v>1.78</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45995.58333333334</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
         <v>2.62</v>
@@ -2117,13 +2117,13 @@
         <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
         <v>1.4</v>
@@ -2132,10 +2132,10 @@
         <v>2.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
         <v>4.4</v>
@@ -2153,7 +2153,7 @@
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45995.64583333334</v>
@@ -2212,7 +2212,7 @@
         <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
         <v>3.54</v>
@@ -2224,7 +2224,7 @@
         <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
         <v>3.6</v>
@@ -2233,13 +2233,13 @@
         <v>2.21</v>
       </c>
       <c r="U15" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="V15" t="n">
         <v>4.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
@@ -2248,19 +2248,19 @@
         <v>1.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE15" t="n">
         <v>1.43</v>
@@ -2328,7 +2328,7 @@
         <v>1.38</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="N16" t="n">
         <v>6.65</v>
@@ -2346,13 +2346,13 @@
         <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
         <v>4.75</v>
@@ -2364,13 +2364,13 @@
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
         <v>4.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
         <v>2.46</v>
@@ -2379,19 +2379,19 @@
         <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45995.70833333334</v>
@@ -2453,10 +2453,10 @@
         <v>3.37</v>
       </c>
       <c r="O17" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="Q17" t="n">
         <v>4.3</v>
@@ -2465,22 +2465,22 @@
         <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="T17" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
         <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
         <v>1.3</v>
@@ -2495,22 +2495,22 @@
         <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AD17" t="n">
         <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45995.8125</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O10" t="n">
         <v>3.25</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3</v>
       </c>
       <c r="P10" t="n">
         <v>2.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>9.48</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
         <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.37</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
         <v>1.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
         <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>1.45</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="Z10" t="n">
         <v>3</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>1.45</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
         <v>3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1858,10 +1858,10 @@
         <v>1.69</v>
       </c>
       <c r="O12" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
         <v>2.05</v>
@@ -1870,13 +1870,13 @@
         <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="T12" t="n">
         <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
         <v>6</v>
@@ -1885,37 +1885,37 @@
         <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
         <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.58</v>
+        <v>3.93</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45995.58333333334</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2444,34 +2444,34 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.37</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P17" t="n">
         <v>2.19</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
         <v>7</v>
@@ -2480,37 +2480,37 @@
         <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
         <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC17" t="n">
         <v>3.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45995.8125</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>1.45</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
         <v>3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>1.45</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="Z11" t="n">
         <v>3</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -2444,19 +2444,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
         <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="O17" t="n">
         <v>2.7</v>
       </c>
       <c r="P17" t="n">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
         <v>4.35</v>
@@ -2468,19 +2468,19 @@
         <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W17" t="n">
         <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>1.3</v>
@@ -2495,10 +2495,10 @@
         <v>1.78</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE17" t="n">
         <v>1.81</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="P10" t="n">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
         <v>3.7</v>
@@ -1635,31 +1635,31 @@
         <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
         <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
         <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC10" t="n">
         <v>4.2</v>
@@ -1668,16 +1668,16 @@
         <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AF10" t="n">
         <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1858,13 +1858,13 @@
         <v>1.69</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>5.53</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="R12" t="n">
         <v>1.33</v>
@@ -1873,49 +1873,49 @@
         <v>2.91</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
         <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W12" t="n">
         <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.93</v>
+        <v>3.68</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45995.58333333334</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2325,37 +2325,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>6.65</v>
+        <v>6.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="Q16" t="n">
         <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="T16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U16" t="n">
         <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="W16" t="n">
         <v>1.16</v>
@@ -2364,25 +2364,25 @@
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
         <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="n">
         <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
         <v>2.2</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.65</v>
+        <v>3.37</v>
       </c>
       <c r="O17" t="n">
         <v>2.7</v>
@@ -2489,10 +2489,10 @@
         <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
         <v>3.44</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="N2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O2" t="n">
-        <v>5.22</v>
+        <v>7.9</v>
       </c>
       <c r="P2" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
@@ -683,7 +683,7 @@
         <v>2.85</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
         <v>1.42</v>
@@ -698,31 +698,31 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
         <v>1.94</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AD2" t="n">
         <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF2" t="n">
         <v>1.69</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH2" t="n">
         <v>1.05</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
         <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>6.16</v>
       </c>
       <c r="R6" t="n">
         <v>1.46</v>
@@ -1159,7 +1159,7 @@
         <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="U6" t="n">
         <v>1.3</v>
@@ -1168,40 +1168,40 @@
         <v>8.699999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
         <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AD6" t="n">
         <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45995.4375</v>
@@ -1418,10 +1418,10 @@
         <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
         <v>5</v>
@@ -1635,13 +1635,13 @@
         <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U10" t="n">
         <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>7.3</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
         <v>1.06</v>
@@ -1653,7 +1653,7 @@
         <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="AA10" t="n">
         <v>2.05</v>
@@ -1730,25 +1730,25 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="O11" t="n">
-        <v>6.4</v>
+        <v>6.67</v>
       </c>
       <c r="P11" t="n">
         <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
         <v>2.66</v>
@@ -1760,7 +1760,7 @@
         <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="W11" t="n">
         <v>1.05</v>
@@ -1769,16 +1769,16 @@
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
         <v>3.52</v>
@@ -1790,7 +1790,7 @@
         <v>2.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
         <v>1.22</v>
@@ -1858,31 +1858,31 @@
         <v>1.69</v>
       </c>
       <c r="O12" t="n">
-        <v>5.53</v>
+        <v>4.82</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="U12" t="n">
         <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -1891,7 +1891,7 @@
         <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AA12" t="n">
         <v>1.85</v>
@@ -1977,46 +1977,46 @@
         <v>14</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC13" t="n">
         <v>1.7</v>
@@ -2025,16 +2025,16 @@
         <v>2.02</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45995.625</v>
@@ -2087,37 +2087,37 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="M14" t="n">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>4.96</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="W14" t="n">
         <v>1.01</v>
@@ -2126,34 +2126,34 @@
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.4</v>
+        <v>4.17</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AF14" t="n">
         <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45995.64583333334</v>
@@ -2325,19 +2325,19 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="N16" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="O16" t="n">
         <v>1.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="Q16" t="n">
         <v>5</v>
@@ -2483,7 +2483,7 @@
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
         <v>3.05</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S15" t="n">
         <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V15" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45995.66666666666</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.09</v>
+        <v>1.82</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.37</v>
+        <v>3.78</v>
       </c>
       <c r="O17" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="P17" t="n">
         <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
         <v>1.43</v>
@@ -2474,7 +2474,7 @@
         <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
         <v>1.02</v>
@@ -2489,13 +2489,13 @@
         <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="AD17" t="n">
         <v>1.23</v>
@@ -2510,7 +2510,7 @@
         <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45995.8125</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -668,7 +668,7 @@
         <v>1.41</v>
       </c>
       <c r="O2" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
         <v>2.22</v>
@@ -698,7 +698,7 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
         <v>3.5</v>
@@ -710,22 +710,22 @@
         <v>1.94</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AD2" t="n">
         <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AG2" t="n">
         <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45995.33333333334</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1144,19 +1144,19 @@
         <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.16</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T6" t="n">
         <v>3.16</v>
@@ -1171,7 +1171,7 @@
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
         <v>1.35</v>
@@ -1186,13 +1186,13 @@
         <v>1.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="AD6" t="n">
         <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AF6" t="n">
         <v>1.65</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9</v>
+        <v>1.53</v>
       </c>
       <c r="O10" t="n">
-        <v>3.12</v>
+        <v>6.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.3</v>
       </c>
-      <c r="V10" t="n">
-        <v>9</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z10" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.49</v>
+        <v>1.08</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.53</v>
+        <v>2.9</v>
       </c>
       <c r="O11" t="n">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
         <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.07</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
-        <v>2.84</v>
+        <v>3.16</v>
       </c>
       <c r="U11" t="n">
         <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.05</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1858,22 +1858,22 @@
         <v>1.69</v>
       </c>
       <c r="O12" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>3.23</v>
       </c>
       <c r="T12" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
         <v>1.44</v>
@@ -1885,10 +1885,10 @@
         <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
         <v>3.7</v>
@@ -1906,10 +1906,10 @@
         <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
         <v>1.18</v>
@@ -2099,37 +2099,37 @@
         <v>2.63</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.96</v>
+        <v>4.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="AA14" t="n">
         <v>2.17</v>
@@ -2138,22 +2138,22 @@
         <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.17</v>
+        <v>4.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45995.64583333334</v>
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="N16" t="n">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="O16" t="n">
         <v>1.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="R16" t="n">
         <v>1.26</v>
@@ -2349,7 +2349,7 @@
         <v>3.66</v>
       </c>
       <c r="T16" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
         <v>1.66</v>
@@ -2364,25 +2364,25 @@
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
         <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB16" t="n">
         <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
         <v>1.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AF16" t="n">
         <v>2.2</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.82</v>
+        <v>2.09</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.78</v>
+        <v>3.37</v>
       </c>
       <c r="O17" t="n">
         <v>2.69</v>
@@ -2489,10 +2489,10 @@
         <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
         <v>3.7</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3.89</v>
+        <v>4.2</v>
       </c>
       <c r="N2" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="P2" t="n">
         <v>2.22</v>
@@ -698,25 +698,25 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
         <v>3.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
         <v>1.94</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AF2" t="n">
         <v>1.68</v>
@@ -725,7 +725,7 @@
         <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45995.33333333334</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>6.33</v>
       </c>
       <c r="R6" t="n">
         <v>1.47</v>
@@ -1180,19 +1180,19 @@
         <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="AD6" t="n">
         <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AF6" t="n">
         <v>1.65</v>
@@ -1201,7 +1201,7 @@
         <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45995.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.53</v>
+        <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
         <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="U10" t="n">
         <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="W10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.05</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>1.45</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="P11" t="n">
         <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>3.16</v>
+        <v>2.84</v>
       </c>
       <c r="U11" t="n">
         <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.02</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -784,7 +784,7 @@
         <v>2.94</v>
       </c>
       <c r="N3" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -903,7 +903,7 @@
         <v>2.82</v>
       </c>
       <c r="N4" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9</v>
+        <v>1.45</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="P10" t="n">
         <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
-        <v>3.16</v>
+        <v>2.84</v>
       </c>
       <c r="U10" t="n">
         <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.02</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.9</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>6.67</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.07</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.84</v>
+        <v>3.22</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.05</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.77</v>
       </c>
-      <c r="AC11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1858,19 +1858,19 @@
         <v>1.69</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>5.53</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q12" t="n">
         <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.23</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
         <v>2.5</v>
@@ -1885,19 +1885,19 @@
         <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
         <v>3.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
         <v>2.7</v>
@@ -1906,10 +1906,10 @@
         <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG12" t="n">
         <v>1.18</v>
@@ -1977,13 +1977,13 @@
         <v>14</v>
       </c>
       <c r="O13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P13" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R13" t="n">
         <v>1.15</v>
@@ -2010,7 +2010,7 @@
         <v>1.04</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
         <v>1.24</v>
@@ -2019,10 +2019,10 @@
         <v>3.34</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AE13" t="n">
         <v>1.77</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.2</v>
+        <v>5.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45995.64583333334</v>
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="O15" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="P15" t="n">
         <v>2.29</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="R15" t="n">
         <v>1.22</v>
@@ -2230,37 +2230,37 @@
         <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V15" t="n">
         <v>4.65</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z15" t="n">
         <v>5.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE15" t="n">
         <v>1.38</v>
@@ -2272,7 +2272,7 @@
         <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45995.66666666666</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>6.45</v>
+        <v>6.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.85</v>
@@ -2340,7 +2340,7 @@
         <v>2.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
         <v>1.26</v>
@@ -2349,10 +2349,10 @@
         <v>3.66</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
         <v>4.9</v>
@@ -2370,28 +2370,28 @@
         <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
         <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AD16" t="n">
         <v>1.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45995.70833333334</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -2349,13 +2349,13 @@
         <v>3.66</v>
       </c>
       <c r="T16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="W16" t="n">
         <v>1.16</v>
@@ -2376,22 +2376,22 @@
         <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
         <v>1.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45995.70833333334</v>
@@ -2444,28 +2444,28 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="T17" t="n">
         <v>2.94</v>
@@ -2474,13 +2474,13 @@
         <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W17" t="n">
         <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
         <v>1.29</v>
@@ -2489,13 +2489,13 @@
         <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AD17" t="n">
         <v>1.23</v>
@@ -2507,10 +2507,10 @@
         <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45995.8125</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4.2</v>
+        <v>3.89</v>
       </c>
       <c r="N2" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="O2" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
         <v>1.94</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45995.33333333334</v>
@@ -784,7 +784,7 @@
         <v>2.94</v>
       </c>
       <c r="N3" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -903,7 +903,7 @@
         <v>2.82</v>
       </c>
       <c r="N4" t="n">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
         <v>3.17</v>
       </c>
       <c r="N5" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="P6" t="n">
         <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.33</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
         <v>1.47</v>
@@ -1174,16 +1174,16 @@
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
         <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.45</v>
+        <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.07</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>2.84</v>
+        <v>3.32</v>
       </c>
       <c r="U10" t="n">
         <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="P11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1864,13 +1864,13 @@
         <v>2.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>3.23</v>
       </c>
       <c r="T12" t="n">
         <v>2.5</v>
@@ -1885,37 +1885,37 @@
         <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD12" t="n">
         <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45995.58333333334</v>
@@ -1977,64 +1977,64 @@
         <v>14</v>
       </c>
       <c r="O13" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="P13" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S13" t="n">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="U13" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="V13" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AB13" t="n">
         <v>3.34</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45995.625</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="M14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T14" t="n">
         <v>3.2</v>
       </c>
-      <c r="N14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="U14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE14" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45995.64583333334</v>
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
         <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="O15" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="P15" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="R15" t="n">
         <v>1.22</v>
@@ -2230,16 +2230,16 @@
         <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V15" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
@@ -2251,16 +2251,16 @@
         <v>5.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE15" t="n">
         <v>1.38</v>
@@ -2272,7 +2272,7 @@
         <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45995.66666666666</v>
@@ -2325,19 +2325,19 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="P16" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="Q16" t="n">
         <v>5</v>
@@ -2349,10 +2349,10 @@
         <v>3.66</v>
       </c>
       <c r="T16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
         <v>4.95</v>
@@ -2370,13 +2370,13 @@
         <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB16" t="n">
         <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD16" t="n">
         <v>1.62</v>
@@ -2391,7 +2391,7 @@
         <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45995.70833333334</v>
@@ -2444,25 +2444,25 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="O17" t="n">
-        <v>2.72</v>
+        <v>2.49</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
         <v>2.59</v>
@@ -2474,13 +2474,13 @@
         <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
         <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
         <v>1.29</v>
@@ -2489,13 +2489,13 @@
         <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.44</v>
+        <v>3.64</v>
       </c>
       <c r="AD17" t="n">
         <v>1.23</v>
@@ -2504,13 +2504,13 @@
         <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
         <v>1.35</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45995.8125</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -671,37 +671,37 @@
         <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
         <v>6.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="AA2" t="n">
         <v>1.76</v>
@@ -713,19 +713,19 @@
         <v>3.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45995.33333333334</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1147,25 +1147,25 @@
         <v>2.15</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>3.16</v>
+        <v>3.31</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
@@ -1174,10 +1174,10 @@
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA6" t="n">
         <v>2.15</v>
@@ -1186,22 +1186,22 @@
         <v>1.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45995.4375</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>4.21</v>
+        <v>4.7</v>
       </c>
       <c r="N7" t="n">
-        <v>7.55</v>
+        <v>9</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9</v>
+        <v>1.53</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>5.13</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>2.03</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
-        <v>3.32</v>
+        <v>2.84</v>
       </c>
       <c r="U10" t="n">
         <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.65</v>
+        <v>1.08</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.53</v>
+        <v>2.9</v>
       </c>
       <c r="O11" t="n">
-        <v>6.4</v>
+        <v>3.54</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.07</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.66</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.28</v>
+        <v>3.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1858,10 +1858,10 @@
         <v>1.69</v>
       </c>
       <c r="O12" t="n">
-        <v>5.53</v>
+        <v>4.82</v>
       </c>
       <c r="P12" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
         <v>1.94</v>
@@ -1873,7 +1873,7 @@
         <v>3.23</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U12" t="n">
         <v>1.44</v>
@@ -1891,7 +1891,7 @@
         <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.72</v>
+        <v>3.96</v>
       </c>
       <c r="AA12" t="n">
         <v>1.85</v>
@@ -1900,22 +1900,22 @@
         <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.4</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45995.58333333334</v>
@@ -1977,13 +1977,13 @@
         <v>14</v>
       </c>
       <c r="O13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.75</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R13" t="n">
         <v>1.16</v>
@@ -2025,16 +2025,16 @@
         <v>2.02</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
         <v>1.05</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45995.625</v>
@@ -2105,28 +2105,28 @@
         <v>4.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
         <v>3.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
         <v>8.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
         <v>2.7</v>
@@ -2147,7 +2147,7 @@
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>
@@ -2325,40 +2325,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="O16" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="Q16" t="n">
         <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="T16" t="n">
         <v>2.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V16" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
@@ -2367,25 +2367,25 @@
         <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB16" t="n">
         <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AD16" t="n">
         <v>1.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AG16" t="n">
         <v>1.18</v>
@@ -2453,16 +2453,16 @@
         <v>3.37</v>
       </c>
       <c r="O17" t="n">
-        <v>2.49</v>
+        <v>2.68</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
         <v>2.59</v>
@@ -2471,19 +2471,19 @@
         <v>2.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
         <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
         <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
         <v>3.05</v>
@@ -2495,7 +2495,7 @@
         <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="AD17" t="n">
         <v>1.23</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -659,40 +659,40 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6.5</v>
+        <v>7.35</v>
       </c>
       <c r="M2" t="n">
-        <v>3.89</v>
+        <v>4.49</v>
       </c>
       <c r="N2" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="O2" t="n">
         <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>6.45</v>
+        <v>6.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -704,28 +704,28 @@
         <v>3.61</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC2" t="n">
         <v>3.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45995.33333333334</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="O6" t="n">
         <v>2.15</v>
@@ -1153,22 +1153,22 @@
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="T6" t="n">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
@@ -1180,25 +1180,25 @@
         <v>2.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AH6" t="n">
         <v>2.07</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1611,16 +1611,16 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="O10" t="n">
-        <v>5.13</v>
+        <v>6.25</v>
       </c>
       <c r="P10" t="n">
         <v>2.14</v>
@@ -1629,19 +1629,19 @@
         <v>2.03</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
         <v>1.05</v>
@@ -1650,16 +1650,16 @@
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
         <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>3.28</v>
@@ -1668,16 +1668,16 @@
         <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1977,25 +1977,25 @@
         <v>14</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="P13" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="T13" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="U13" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="V13" t="n">
         <v>3.5</v>
@@ -2010,31 +2010,31 @@
         <v>1.05</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AC13" t="n">
         <v>1.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG13" t="n">
         <v>1.05</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45995.625</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -784,7 +784,7 @@
         <v>2.94</v>
       </c>
       <c r="N3" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -903,7 +903,7 @@
         <v>2.82</v>
       </c>
       <c r="N4" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
         <v>3.17</v>
       </c>
       <c r="N5" t="n">
-        <v>4.78</v>
+        <v>4.77</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7</v>
+        <v>5.01</v>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45995.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.43</v>
+        <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>6.25</v>
+        <v>3.54</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.03</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="T10" t="n">
-        <v>2.65</v>
+        <v>3.16</v>
       </c>
       <c r="U10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.42</v>
       </c>
-      <c r="V10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>1.43</v>
       </c>
       <c r="O11" t="n">
-        <v>3.54</v>
+        <v>6.25</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>2.03</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>3.16</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.02</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -2090,25 +2090,25 @@
         <v>1.85</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3</v>
+        <v>4.19</v>
       </c>
       <c r="O14" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="P14" t="n">
         <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="T14" t="n">
         <v>3.2</v>
@@ -2117,43 +2117,43 @@
         <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
         <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AC14" t="n">
         <v>4.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45995.64583333334</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.77</v>
+        <v>4.68</v>
       </c>
       <c r="R8" t="n">
         <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T8" t="n">
-        <v>3.71</v>
+        <v>3.42</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="V8" t="n">
-        <v>8.539999999999999</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z8" t="n">
         <v>2.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
         <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9</v>
+        <v>1.43</v>
       </c>
       <c r="O10" t="n">
-        <v>3.54</v>
+        <v>6.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>2.03</v>
       </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>3.16</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.02</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="N11" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="O11" t="n">
-        <v>6.25</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="AB11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.42</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.06</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1849,19 +1849,19 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.3</v>
+        <v>5.27</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>4.04</v>
       </c>
       <c r="N12" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="O12" t="n">
-        <v>4.82</v>
+        <v>5.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
         <v>1.94</v>
@@ -1873,16 +1873,16 @@
         <v>3.23</v>
       </c>
       <c r="T12" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
@@ -1891,13 +1891,13 @@
         <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.96</v>
+        <v>3.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC12" t="n">
         <v>3</v>
@@ -1906,16 +1906,16 @@
         <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.16</v>
+        <v>2.41</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45995.58333333334</v>
@@ -2206,70 +2206,70 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="O15" t="n">
-        <v>3.31</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="R15" t="n">
         <v>1.22</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V15" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.5</v>
+        <v>6.11</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AH15" t="n">
         <v>1.4</v>
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>4.82</v>
       </c>
       <c r="N16" t="n">
-        <v>6.57</v>
+        <v>6.49</v>
       </c>
       <c r="O16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="P16" t="n">
         <v>2.63</v>
@@ -2343,49 +2343,49 @@
         <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="T16" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U16" t="n">
         <v>1.63</v>
       </c>
       <c r="V16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="W16" t="n">
         <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
         <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
         <v>1.18</v>
@@ -2444,55 +2444,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.37</v>
+        <v>3.76</v>
       </c>
       <c r="O17" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
         <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="T17" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
         <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
         <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AC17" t="n">
         <v>3.6</v>
@@ -2504,13 +2504,13 @@
         <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45995.8125</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -784,7 +784,7 @@
         <v>2.94</v>
       </c>
       <c r="N3" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -903,7 +903,7 @@
         <v>2.82</v>
       </c>
       <c r="N4" t="n">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
         <v>3.17</v>
       </c>
       <c r="N5" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1254,28 +1254,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>5.01</v>
+        <v>4.7</v>
       </c>
       <c r="N7" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="P7" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="T7" t="n">
         <v>2.53</v>
@@ -1296,13 +1296,13 @@
         <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
         <v>2.74</v>
@@ -1317,10 +1317,10 @@
         <v>1.59</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45995.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="N10" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="O10" t="n">
-        <v>6.25</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA10" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="AB10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.42</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.06</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>2.99</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>6.25</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.09</v>
+        <v>2.03</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.33</v>
       </c>
-      <c r="V11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W11" t="n">
+      <c r="Z11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.06</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.42</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -2325,19 +2325,19 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="N16" t="n">
-        <v>6.49</v>
+        <v>6.43</v>
       </c>
       <c r="O16" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="Q16" t="n">
         <v>5</v>
@@ -2346,22 +2346,22 @@
         <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="T16" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="W16" t="n">
         <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
         <v>1.15</v>
@@ -2370,28 +2370,28 @@
         <v>4.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="AC16" t="n">
         <v>2.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45995.70833333334</v>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="N17" t="n">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="O17" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
         <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
         <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45995.8125</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -659,40 +659,40 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7.35</v>
+        <v>6.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4.49</v>
+        <v>3.89</v>
       </c>
       <c r="N2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="O2" t="n">
         <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -701,31 +701,31 @@
         <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45995.33333333334</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.99</v>
+        <v>1.69</v>
       </c>
       <c r="M3" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3.73</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA3" t="n">
         <v>2.75</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.71</v>
+        <v>2.23</v>
       </c>
       <c r="M5" t="n">
-        <v>3.17</v>
+        <v>2.6</v>
       </c>
       <c r="N5" t="n">
-        <v>4.78</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA5" t="n">
         <v>2.6</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="N6" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
         <v>2.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45995.4375</v>
@@ -1263,13 +1263,13 @@
         <v>9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="P7" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>1.33</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="M10" t="n">
-        <v>2.99</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>2.63</v>
+        <v>1.53</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>6.75</v>
       </c>
       <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.09</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.88</v>
+        <v>3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>2.54</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>3.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.43</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.03</v>
+        <v>3.38</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.42</v>
       </c>
-      <c r="V11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.27</v>
+        <v>4.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4.04</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="O12" t="n">
-        <v>5.8</v>
+        <v>5.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
@@ -1873,10 +1873,10 @@
         <v>3.23</v>
       </c>
       <c r="T12" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="U12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
         <v>6</v>
@@ -1888,34 +1888,34 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z12" t="n">
         <v>3.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.41</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45995.58333333334</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="M13" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="N13" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.3</v>
+        <v>6.57</v>
       </c>
       <c r="R13" t="n">
         <v>1.17</v>
       </c>
       <c r="S13" t="n">
-        <v>4.75</v>
+        <v>3.96</v>
       </c>
       <c r="T13" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="V13" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="W13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.6</v>
+        <v>6.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AC13" t="n">
         <v>1.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AE13" t="n">
         <v>1.78</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
         <v>1.05</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45995.625</v>
@@ -2087,28 +2087,28 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>4.19</v>
+        <v>3.84</v>
       </c>
       <c r="O14" t="n">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="P14" t="n">
         <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="T14" t="n">
         <v>3.2</v>
@@ -2117,43 +2117,43 @@
         <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
         <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
         <v>4.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45995.64583333334</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="M16" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
       <c r="O16" t="n">
         <v>1.85</v>
@@ -2340,25 +2340,25 @@
         <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
         <v>3.9</v>
       </c>
       <c r="T16" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V16" t="n">
         <v>4.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
@@ -2367,19 +2367,19 @@
         <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="n">
         <v>2.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AE16" t="n">
         <v>1.64</v>
@@ -2388,10 +2388,10 @@
         <v>2.12</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45995.70833333334</v>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="M17" t="n">
-        <v>3.26</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.58</v>
+        <v>3.37</v>
       </c>
       <c r="O17" t="n">
         <v>2.7</v>
       </c>
       <c r="P17" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
         <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
         <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="W17" t="n">
         <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
         <v>3.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45995.8125</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -787,34 +787,34 @@
         <v>5.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
         <v>1.55</v>
@@ -829,22 +829,22 @@
         <v>1.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45995.36458333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.5</v>
+        <v>2.54</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>3.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.53</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>6.75</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>3.38</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="T10" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.54</v>
+        <v>5.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.01</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>1.53</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>6.75</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.38</v>
+        <v>1.98</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="T11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3.2</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI17"/>
+  <dimension ref="A1:AI18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,76 +1135,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>8.800000000000001</v>
+        <v>6.84</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>45995.4375</v>
+        <v>45995.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,76 +1254,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7</v>
+        <v>3.16</v>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.53</v>
+        <v>3.31</v>
       </c>
       <c r="U7" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="V7" t="n">
-        <v>6.15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z7" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH7" t="n">
-        <v>3.18</v>
+        <v>2.12</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>45995.45833333334</v>
+        <v>45995.4375</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,76 +1373,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>2.96</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>45995.5</v>
+        <v>45995.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,80 +1607,80 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.38</v>
+        <v>4.81</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="U10" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="V10" t="n">
-        <v>7.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="AA10" t="n">
         <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.74</v>
+        <v>4.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45995.54166666666</v>
+        <v>45995.5</v>
       </c>
     </row>
     <row r="11">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.5</v>
+        <v>2.54</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.53</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>6.75</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.98</v>
+        <v>3.38</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.3</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Z12" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>45995.58333333334</v>
+        <v>45995.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.14</v>
+        <v>4.3</v>
       </c>
       <c r="M13" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>11</v>
+        <v>1.69</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>5.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.89</v>
+        <v>2.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.57</v>
+        <v>2.08</v>
       </c>
       <c r="R13" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.96</v>
+        <v>3.23</v>
       </c>
       <c r="T13" t="n">
-        <v>1.88</v>
+        <v>2.59</v>
       </c>
       <c r="U13" t="n">
-        <v>1.88</v>
+        <v>1.49</v>
       </c>
       <c r="V13" t="n">
-        <v>3.72</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.15</v>
+        <v>3.74</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.34</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.7</v>
+        <v>2.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.02</v>
+        <v>1.37</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.1</v>
+        <v>1.16</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>45995.625</v>
+        <v>45995.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>11</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD14" t="n">
         <v>2.02</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="AE14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.05</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.86</v>
+        <v>4.1</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>45995.64583333334</v>
+        <v>45995.625</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.64</v>
+        <v>2.02</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.19</v>
       </c>
       <c r="N15" t="n">
-        <v>2.07</v>
+        <v>3.84</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="P15" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.76</v>
+        <v>4.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="T15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE15" t="n">
         <v>2.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AF15" t="n">
         <v>1.67</v>
       </c>
-      <c r="V15" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.85</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.86</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>45995.66666666666</v>
+        <v>45995.64583333334</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.47</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>6.41</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.85</v>
+        <v>3.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>2.73</v>
       </c>
       <c r="R16" t="n">
         <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="V16" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.85</v>
+        <v>6.23</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.12</v>
+        <v>3.02</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>45995.70833333334</v>
+        <v>45995.66666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2403,116 +2403,235 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI17" s="3" t="n">
+        <v>45995.70833333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Cruzeiro</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Botafogo</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>2.09</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M18" t="n">
         <v>2.9</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N18" t="n">
         <v>3.37</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O18" t="n">
         <v>2.7</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P18" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q18" t="n">
         <v>3.9</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>1.43</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>2.62</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>2.8</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>1.38</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V18" t="n">
         <v>7.7</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W18" t="n">
         <v>1.07</v>
       </c>
-      <c r="X17" t="n">
+      <c r="X18" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y18" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="Z18" t="n">
         <v>3.05</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA18" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AB18" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AC18" t="n">
         <v>3.44</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AD18" t="n">
         <v>1.29</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AE18" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AF18" t="n">
         <v>1.9</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AG18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AH18" t="n">
         <v>1.74</v>
       </c>
-      <c r="AI17" s="3" t="n">
+      <c r="AI18" s="3" t="n">
         <v>45995.8125</v>
       </c>
     </row>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -659,37 +659,37 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>3.89</v>
+        <v>4.81</v>
       </c>
       <c r="N2" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="O2" t="n">
         <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="U2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V2" t="n">
-        <v>6.45</v>
+        <v>6.4</v>
       </c>
       <c r="W2" t="n">
         <v>1.05</v>
@@ -704,25 +704,25 @@
         <v>3.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH2" t="n">
         <v>1.05</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>5.26</v>
       </c>
       <c r="O7" t="n">
         <v>2.4</v>
@@ -1275,52 +1275,52 @@
         <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T7" t="n">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
         <v>1.28</v>
       </c>
       <c r="V7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
         <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45995.4375</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="O12" t="n">
         <v>6.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="T12" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
         <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
         <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45995.54166666666</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -645,17 +645,17 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -774,17 +774,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="O3" t="n">
         <v>2.4</v>
@@ -793,10 +793,10 @@
         <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.78</v>
+        <v>6.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S3" t="n">
         <v>2.18</v>
@@ -817,16 +817,16 @@
         <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
         <v>5.85</v>
@@ -841,7 +841,7 @@
         <v>1.43</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AH3" t="n">
         <v>1.98</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -903,7 +903,7 @@
         <v>2.82</v>
       </c>
       <c r="N4" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45995.40625</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1382,40 +1382,40 @@
         <v>9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="P8" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>2.91</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="AA8" t="n">
         <v>1.72</v>
@@ -1424,25 +1424,25 @@
         <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.16</v>
+        <v>2.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.18</v>
+        <v>3.7</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>45995.45833333334</v>
+        <v>45995.4375</v>
       </c>
     </row>
     <row r="9">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>4.81</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.45</v>
+        <v>4.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
         <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.81</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.51</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V10" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AC10" t="n">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.54</v>
+        <v>5.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.01</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>1.53</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>6.75</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.38</v>
+        <v>1.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.81</v>
       </c>
       <c r="T11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3.2</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="AD11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.19</v>
       </c>
-      <c r="AE11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.41</v>
+        <v>1.06</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7.4</v>
+        <v>2.54</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>3.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.42</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>6.75</v>
+        <v>3.52</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>3.42</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.4</v>
       </c>
-      <c r="V12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z12" t="n">
-        <v>3.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1977,13 +1977,13 @@
         <v>1.69</v>
       </c>
       <c r="O13" t="n">
-        <v>5.25</v>
+        <v>4.94</v>
       </c>
       <c r="P13" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="R13" t="n">
         <v>1.3</v>
@@ -1992,25 +1992,25 @@
         <v>3.23</v>
       </c>
       <c r="T13" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
         <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA13" t="n">
         <v>1.85</v>
@@ -2019,22 +2019,22 @@
         <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
         <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45995.58333333334</v>
@@ -2096,13 +2096,13 @@
         <v>11</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="P14" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.57</v>
+        <v>7.9</v>
       </c>
       <c r="R14" t="n">
         <v>1.17</v>
@@ -2111,10 +2111,10 @@
         <v>3.96</v>
       </c>
       <c r="T14" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="V14" t="n">
         <v>3.72</v>
@@ -2126,7 +2126,7 @@
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z14" t="n">
         <v>6.15</v>
@@ -2144,16 +2144,16 @@
         <v>2.02</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45995.625</v>
@@ -2215,37 +2215,37 @@
         <v>3.84</v>
       </c>
       <c r="O15" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="U15" t="n">
         <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
         <v>2.7</v>
@@ -2263,16 +2263,16 @@
         <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45995.64583333334</v>
@@ -2444,31 +2444,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M17" t="n">
         <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>6.41</v>
+        <v>6.43</v>
       </c>
       <c r="O17" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="U17" t="n">
         <v>1.63</v>
@@ -2477,7 +2477,7 @@
         <v>4.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
@@ -2486,31 +2486,31 @@
         <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="AA17" t="n">
         <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AG17" t="n">
         <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45995.70833333334</v>
@@ -2581,22 +2581,22 @@
         <v>3.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="T18" t="n">
         <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
         <v>7.7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
@@ -2617,19 +2617,19 @@
         <v>3.44</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45995.8125</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1002,17 +1002,17 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1118,20 +1118,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="N7" t="n">
-        <v>5.26</v>
+        <v>9</v>
       </c>
       <c r="O7" t="n">
-        <v>2.4</v>
+        <v>1.69</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>2.27</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.62</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>9.5</v>
+        <v>6.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45995.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,16 +1347,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>5.26</v>
       </c>
       <c r="O8" t="n">
-        <v>1.69</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.27</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z8" t="n">
         <v>2.62</v>
       </c>
-      <c r="U8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.7</v>
+        <v>2.04</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.4375</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.81</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V9" t="n">
+        <v>10</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.51</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V9" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AC9" t="n">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
         <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.5</v>
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="O11" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
         <v>1.06</v>
@@ -1769,34 +1769,34 @@
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,16 +1228,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>5.26</v>
       </c>
       <c r="O7" t="n">
-        <v>1.69</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.27</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="T7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.62</v>
       </c>
-      <c r="U7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.7</v>
+        <v>2.04</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45995.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V8" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC8" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.4375</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>5.84</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.33</v>
+        <v>2.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.45</v>
+        <v>5.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.13</v>
+        <v>2.31</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1594,20 +1594,20 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1713,20 +1713,20 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1849,70 +1849,70 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.54</v>
+        <v>2.94</v>
       </c>
       <c r="M12" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
         <v>1.4</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1964,23 +1964,23 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
-        <v>4.94</v>
+        <v>4.84</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
         <v>2.07</v>
@@ -1992,10 +1992,10 @@
         <v>3.23</v>
       </c>
       <c r="T13" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V13" t="n">
         <v>6</v>
@@ -2007,34 +2007,34 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AF13" t="n">
         <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45995.58333333334</v>
@@ -2087,40 +2087,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="M14" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O14" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.9</v>
+        <v>8.68</v>
       </c>
       <c r="R14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="V14" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
@@ -2129,31 +2129,31 @@
         <v>1.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.15</v>
+        <v>6.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.86</v>
+        <v>5.6</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45995.625</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="M15" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="N15" t="n">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>5.43</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T15" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
         <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.03</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45995.64583333334</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="M16" t="n">
         <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O16" t="n">
-        <v>3.26</v>
+        <v>3.53</v>
       </c>
       <c r="P16" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="U16" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="V16" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.23</v>
+        <v>6.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="AG16" t="n">
         <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45995.66666666666</v>
@@ -2444,40 +2444,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>6.43</v>
+        <v>7.22</v>
       </c>
       <c r="O17" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
         <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
         <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="T17" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
-        <v>4.75</v>
+        <v>5.15</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
@@ -2486,31 +2486,31 @@
         <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45995.70833333334</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,99 +1228,99 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC7" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45995.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,16 +1347,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>5.26</v>
       </c>
       <c r="O8" t="n">
-        <v>1.69</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.27</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z8" t="n">
         <v>2.62</v>
       </c>
-      <c r="U8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.7</v>
+        <v>2.04</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45995.4375</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="M9" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.84</v>
+        <v>4.76</v>
       </c>
       <c r="R9" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,99 +1585,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.76</v>
+        <v>5.84</v>
       </c>
       <c r="R10" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="S10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>12</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2.31</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V10" t="n">
-        <v>11</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.5</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2070,20 +2070,20 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2308,20 +2308,20 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P18" t="n">
         <v>2.09</v>
       </c>
-      <c r="M18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q18" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="W18" t="n">
         <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AA18" t="n">
         <v>2.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.44</v>
+        <v>3.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45995.8125</v>

--- a/jogos_2025-12-04.xlsx
+++ b/jogos_2025-12-04.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.76</v>
+        <v>5.84</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>12</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE9" t="n">
         <v>2.31</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V9" t="n">
-        <v>11</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45995.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,99 +1585,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.84</v>
+        <v>4.76</v>
       </c>
       <c r="R10" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="T10" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45995.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,22 +1704,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>2.94</v>
       </c>
       <c r="M11" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>1.42</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.94</v>
+        <v>3.04</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45995.54166666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,22 +1823,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.94</v>
+        <v>7</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>1.42</v>
       </c>
       <c r="O12" t="n">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.04</v>
+        <v>1.94</v>
       </c>
       <c r="R12" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.36</v>
+        <v>2.85</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.62</v>
+        <v>3.34</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45995.54166666666</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="M18" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="N18" t="n">
-        <v>4.82</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.7</v>
+        <v>5.03</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W18" t="n">
         <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45995.8125</v>
